--- a/Лаб.работа/PKP4 (расчет кинематических и силовых характеристик ПКП)/dannye/Var1.xlsx
+++ b/Лаб.работа/PKP4 (расчет кинематических и силовых характеристик ПКП)/dannye/Var1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hulumulu\Desktop\Никита\Лаб.работа\PKP4 (расчет кинематических и силовых характеристик ПКП)\dannye\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\PKP4 (расчет кинематических и силовых характеристик ПКП)\dannye\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A6EF86-02D4-4A91-A87C-3B95A2C1A5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6C7004-C3F9-485B-99F7-959DA22423BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19230" yWindow="1065" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="L1" sheetId="1" r:id="rId1"/>
@@ -515,9 +515,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -555,9 +555,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -590,26 +590,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -642,26 +625,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -836,9 +802,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="11">
         <v>4</v>
       </c>
@@ -857,7 +823,7 @@
       <c r="N1" s="49"/>
       <c r="O1" s="49"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
         <v>6</v>
       </c>
@@ -876,7 +842,7 @@
       <c r="N2" s="50"/>
       <c r="O2" s="50"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>7</v>
       </c>
@@ -895,7 +861,7 @@
       <c r="N3" s="51"/>
       <c r="O3" s="51"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>10</v>
       </c>
@@ -914,7 +880,7 @@
       <c r="N4" s="52"/>
       <c r="O4" s="52"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -937,7 +903,7 @@
       <c r="N5" s="54"/>
       <c r="O5" s="55"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -960,15 +926,15 @@
       <c r="N6" s="26"/>
       <c r="O6" s="27"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>6</v>
@@ -983,7 +949,7 @@
       <c r="N7" s="26"/>
       <c r="O7" s="27"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1006,7 +972,7 @@
       <c r="N8" s="26"/>
       <c r="O8" s="27"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>0</v>
       </c>
@@ -1029,7 +995,7 @@
       <c r="N9" s="29"/>
       <c r="O9" s="30"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>2</v>
       </c>
@@ -1049,7 +1015,7 @@
       <c r="N10" s="32"/>
       <c r="O10" s="33"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>3</v>
       </c>
@@ -1067,7 +1033,7 @@
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>4</v>
       </c>
@@ -1085,7 +1051,7 @@
       <c r="N12" s="35"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>5</v>
       </c>
@@ -1103,7 +1069,7 @@
       <c r="N13" s="35"/>
       <c r="O13" s="36"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>1</v>
       </c>
@@ -1121,9 +1087,9 @@
       <c r="N14" s="35"/>
       <c r="O14" s="36"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="4">
         <v>3</v>
@@ -1139,7 +1105,7 @@
       <c r="N15" s="35"/>
       <c r="O15" s="36"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>0</v>
       </c>
@@ -1157,7 +1123,7 @@
       <c r="N16" s="35"/>
       <c r="O16" s="36"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>0</v>
       </c>
@@ -1175,7 +1141,7 @@
       <c r="N17" s="38"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>4</v>
       </c>
@@ -1198,7 +1164,7 @@
       <c r="N18" s="41"/>
       <c r="O18" s="42"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>1</v>
       </c>
@@ -1219,7 +1185,7 @@
       <c r="N19" s="44"/>
       <c r="O19" s="45"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>3</v>
       </c>
@@ -1240,7 +1206,7 @@
       <c r="N20" s="44"/>
       <c r="O20" s="45"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>2</v>
       </c>
@@ -1261,7 +1227,7 @@
       <c r="N21" s="44"/>
       <c r="O21" s="45"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>5</v>
       </c>
@@ -1282,7 +1248,7 @@
       <c r="N22" s="44"/>
       <c r="O22" s="45"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>2</v>
       </c>
@@ -1303,7 +1269,7 @@
       <c r="N23" s="44"/>
       <c r="O23" s="45"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>5</v>
       </c>
@@ -1324,7 +1290,7 @@
       <c r="N24" s="44"/>
       <c r="O24" s="45"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>1</v>
       </c>
@@ -1345,7 +1311,7 @@
       <c r="N25" s="44"/>
       <c r="O25" s="45"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>4</v>
       </c>
@@ -1366,7 +1332,7 @@
       <c r="N26" s="44"/>
       <c r="O26" s="45"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>2</v>
       </c>
@@ -1387,7 +1353,7 @@
       <c r="N27" s="44"/>
       <c r="O27" s="45"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>0</v>
       </c>
@@ -1408,7 +1374,7 @@
       <c r="N28" s="47"/>
       <c r="O28" s="48"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>-10</v>
       </c>
@@ -1434,7 +1400,7 @@
       <c r="N29" s="17"/>
       <c r="O29" s="18"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>-10</v>
       </c>
@@ -1458,7 +1424,7 @@
       <c r="N30" s="20"/>
       <c r="O30" s="21"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>-10</v>
       </c>
@@ -1482,7 +1448,7 @@
       <c r="N31" s="20"/>
       <c r="O31" s="21"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>-10</v>
       </c>
@@ -1506,7 +1472,7 @@
       <c r="N32" s="20"/>
       <c r="O32" s="21"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>0</v>
       </c>
@@ -1530,7 +1496,7 @@
       <c r="N33" s="23"/>
       <c r="O33" s="24"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>0.97</v>
       </c>
@@ -1583,7 +1549,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1592,7 +1558,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Лаб.работа/PKP4 (расчет кинематических и силовых характеристик ПКП)/dannye/Var1.xlsx
+++ b/Лаб.работа/PKP4 (расчет кинематических и силовых характеристик ПКП)/dannye/Var1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\PKP4 (расчет кинематических и силовых характеристик ПКП)\dannye\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6C7004-C3F9-485B-99F7-959DA22423BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93F9EFC-236C-4E61-8A60-48D0FE97EA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19230" yWindow="1065" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="L1" sheetId="1" r:id="rId1"/>
@@ -364,33 +364,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -400,6 +373,54 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -462,27 +483,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -810,18 +810,18 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="F1" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
+      <c r="F1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
@@ -829,18 +829,18 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
@@ -848,18 +848,18 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -867,18 +867,18 @@
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -890,18 +890,18 @@
       <c r="C5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="55"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="25"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -913,18 +913,18 @@
       <c r="C6" s="2">
         <v>6</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="27"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="18"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -936,18 +936,18 @@
       <c r="C7" s="2">
         <v>4</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="27"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="18"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -959,18 +959,18 @@
       <c r="C8" s="2">
         <v>5</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="27"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="18"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -982,18 +982,18 @@
       <c r="C9" s="2">
         <v>0</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="30"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="37"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
@@ -1002,18 +1002,18 @@
       <c r="B10" s="4">
         <v>0</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="33"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="40"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
@@ -1022,16 +1022,16 @@
       <c r="B11" s="4">
         <v>0</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="36"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="43"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
@@ -1040,16 +1040,16 @@
       <c r="B12" s="4">
         <v>0</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="36"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="43"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
@@ -1058,16 +1058,16 @@
       <c r="B13" s="4">
         <v>0</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="36"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="43"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
@@ -1076,16 +1076,16 @@
       <c r="B14" s="4">
         <v>5</v>
       </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="36"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
@@ -1094,16 +1094,16 @@
       <c r="B15" s="4">
         <v>3</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="36"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="43"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
@@ -1112,16 +1112,16 @@
       <c r="B16" s="4">
         <v>0</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="36"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="43"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
@@ -1130,16 +1130,16 @@
       <c r="B17" s="5">
         <v>0</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="39"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="46"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
@@ -1151,18 +1151,18 @@
       <c r="C18" s="6">
         <v>0</v>
       </c>
-      <c r="F18" s="40" t="s">
+      <c r="F18" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="42"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="49"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
@@ -1174,16 +1174,16 @@
       <c r="C19" s="6">
         <v>0</v>
       </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="45"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="51"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="52"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
@@ -1195,16 +1195,16 @@
       <c r="C20" s="6">
         <v>0</v>
       </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="45"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="52"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
@@ -1216,16 +1216,16 @@
       <c r="C21" s="6">
         <v>0</v>
       </c>
-      <c r="F21" s="43"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="45"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="52"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
@@ -1237,16 +1237,16 @@
       <c r="C22" s="6">
         <v>0</v>
       </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="45"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="52"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
@@ -1258,16 +1258,16 @@
       <c r="C23" s="6">
         <v>0</v>
       </c>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="45"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="52"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
@@ -1279,16 +1279,16 @@
       <c r="C24" s="6">
         <v>0</v>
       </c>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="45"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="52"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
@@ -1300,16 +1300,16 @@
       <c r="C25" s="6">
         <v>0</v>
       </c>
-      <c r="F25" s="43"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="45"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="51"/>
+      <c r="N25" s="51"/>
+      <c r="O25" s="52"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
@@ -1321,16 +1321,16 @@
       <c r="C26" s="6">
         <v>0</v>
       </c>
-      <c r="F26" s="43"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="45"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="52"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
@@ -1342,16 +1342,16 @@
       <c r="C27" s="6">
         <v>0</v>
       </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="44"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="45"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="52"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
@@ -1363,16 +1363,16 @@
       <c r="C28" s="6">
         <v>0</v>
       </c>
-      <c r="F28" s="46"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="48"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="55"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
@@ -1387,18 +1387,18 @@
       <c r="D29" s="8">
         <v>16.399999999999999</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="18"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="28"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
@@ -1411,18 +1411,18 @@
         <v>0</v>
       </c>
       <c r="D30" s="8">
-        <v>19.2</v>
-      </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="21"/>
+        <v>19.3</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="31"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
@@ -1437,16 +1437,16 @@
       <c r="D31" s="8">
         <v>17</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="21"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="31"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
@@ -1459,18 +1459,18 @@
         <v>0</v>
       </c>
       <c r="D32" s="8">
-        <v>19</v>
-      </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="21"/>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="31"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
@@ -1485,16 +1485,16 @@
       <c r="D33" s="9">
         <v>0</v>
       </c>
-      <c r="F33" s="22"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="24"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="34"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
@@ -1527,18 +1527,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="F29:O33"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="F8:O8"/>
+    <mergeCell ref="F9:O9"/>
+    <mergeCell ref="F10:O17"/>
+    <mergeCell ref="F18:O28"/>
     <mergeCell ref="F6:O6"/>
     <mergeCell ref="F1:O1"/>
     <mergeCell ref="F2:O2"/>
     <mergeCell ref="F3:O3"/>
     <mergeCell ref="F4:O4"/>
     <mergeCell ref="F5:O5"/>
-    <mergeCell ref="F29:O33"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="F8:O8"/>
-    <mergeCell ref="F9:O9"/>
-    <mergeCell ref="F10:O17"/>
-    <mergeCell ref="F18:O28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
